--- a/main/ig/StructureDefinition-fr-cda-traitements.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-traitements.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T15:11:12+00:00</t>
+    <t>2026-04-23T15:25:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-traitements.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-traitements.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-23T15:25:59+00:00</t>
+    <t>2026-05-06T07:44:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-traitements.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-traitements.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-06T07:44:21+00:00</t>
+    <t>2026-05-13T14:53:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-traitements.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-traitements.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-13T14:53:03+00:00</t>
+    <t>2026-05-15T08:08:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-traitements.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-traitements.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T09:35:10+00:00</t>
+    <t>2026-06-29T12:53:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-traitements.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-traitements.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2725" uniqueCount="296">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2739" uniqueCount="310">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T12:53:00+00:00</t>
+    <t>2026-06-29T14:20:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -511,6 +511,9 @@
 </t>
   </si>
   <si>
+    <t>Can serve as a target of a linkHtml reference</t>
+  </si>
+  <si>
     <t>Section.classCode</t>
   </si>
   <si>
@@ -700,6 +703,9 @@
     <t>Titre de la section</t>
   </si>
   <si>
+    <t>If valued, it is to be rendered as part of the narrative content of the clinical document body.</t>
+  </si>
+  <si>
     <t>Section.text</t>
   </si>
   <si>
@@ -710,10 +716,25 @@
     <t>Bloc narratif</t>
   </si>
   <si>
+    <t>Also referred to as the CDA Narrative Block</t>
+  </si>
+  <si>
     <t>Section.confidentialityCode</t>
   </si>
   <si>
+    <t>Controls the disclosure of information in this section</t>
+  </si>
+  <si>
+    <t>A value for Section.confidentialityCode overrides the value propagated from StructuredBody.</t>
+  </si>
+  <si>
     <t>Section.languageCode</t>
+  </si>
+  <si>
+    <t>Human language of character data</t>
+  </si>
+  <si>
+    <t>A value for Section.languageCode overrides the value propagated from StructuredBody.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/all-languages</t>
@@ -726,6 +747,15 @@
 </t>
   </si>
   <si>
+    <t>Primary target of the entries recorded in a section</t>
+  </si>
+  <si>
+    <t>Most of the time the subject is the same as the recordTarget, but need not be, for instance when the subject is a fetus observed in an obstetrical ultrasound.</t>
+  </si>
+  <si>
+    <t>The subject participant can be ascribed to a CDA section or a CDA entry. It propagates to nested components, unless overridden. The subject of a document is presumed to be the patient.</t>
+  </si>
+  <si>
     <t>Section.author</t>
   </si>
   <si>
@@ -733,6 +763,9 @@
 </t>
   </si>
   <si>
+    <t>The author participant can be ascribed to a CDA section, where it overrides the value(s) propagated from the CDA header.</t>
+  </si>
+  <si>
     <t>Section.informant</t>
   </si>
   <si>
@@ -740,6 +773,9 @@
 </t>
   </si>
   <si>
+    <t>The informant participant can be ascribed to a CDA section where it overrides the value(s) propagated from the CDA header.</t>
+  </si>
+  <si>
     <t>Section.entry</t>
   </si>
   <si>
@@ -893,6 +929,12 @@
   <si>
     <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/InfrastructureRoot
 </t>
+  </si>
+  <si>
+    <t>Used to nest a Section within a Section</t>
+  </si>
+  <si>
+    <t>Context propagates to nested sections</t>
   </si>
   <si>
     <t>Section.component.nullFlavor</t>
@@ -1269,7 +1311,7 @@
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="13.4296875" customWidth="true" bestFit="true"/>
+    <col min="15" max="15" width="148.87109375" customWidth="true" bestFit="true"/>
     <col min="16" max="16" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
@@ -4308,7 +4350,9 @@
       <c r="K30" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="L30" s="2"/>
+      <c r="L30" t="s" s="2">
+        <v>161</v>
+      </c>
       <c r="M30" s="2"/>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4379,10 +4423,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4416,7 +4460,7 @@
       </c>
       <c r="Q31" s="2"/>
       <c r="R31" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="S31" t="s" s="2">
         <v>74</v>
@@ -4438,7 +4482,7 @@
       </c>
       <c r="Y31" s="2"/>
       <c r="Z31" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>74</v>
@@ -4456,7 +4500,7 @@
         <v>74</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -4476,10 +4520,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4513,7 +4557,7 @@
       </c>
       <c r="Q32" s="2"/>
       <c r="R32" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="S32" t="s" s="2">
         <v>74</v>
@@ -4535,7 +4579,7 @@
       </c>
       <c r="Y32" s="2"/>
       <c r="Z32" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>74</v>
@@ -4553,7 +4597,7 @@
         <v>74</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -4573,10 +4617,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4590,7 +4634,7 @@
         <v>75</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>74</v>
@@ -4602,10 +4646,10 @@
         <v>95</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -4656,7 +4700,7 @@
         <v>74</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -4676,10 +4720,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4693,7 +4737,7 @@
         <v>75</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>74</v>
@@ -4702,13 +4746,13 @@
         <v>74</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -4759,7 +4803,7 @@
         <v>74</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -4779,10 +4823,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -4880,10 +4924,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -4899,7 +4943,7 @@
         <v>75</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>74</v>
@@ -4912,7 +4956,7 @@
       </c>
       <c r="L36" s="2"/>
       <c r="M36" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -4924,7 +4968,7 @@
         <v>74</v>
       </c>
       <c r="S36" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="T36" t="s" s="2">
         <v>74</v>
@@ -4963,7 +5007,7 @@
         <v>74</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -4983,17 +5027,17 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E37" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F37" t="s" s="2">
         <v>75</v>
@@ -5002,7 +5046,7 @@
         <v>75</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>74</v>
@@ -5015,7 +5059,7 @@
       </c>
       <c r="L37" s="2"/>
       <c r="M37" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5027,7 +5071,7 @@
         <v>74</v>
       </c>
       <c r="S37" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="T37" t="s" s="2">
         <v>74</v>
@@ -5066,7 +5110,7 @@
         <v>74</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -5086,17 +5130,17 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E38" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F38" t="s" s="2">
         <v>80</v>
@@ -5118,7 +5162,7 @@
       </c>
       <c r="L38" s="2"/>
       <c r="M38" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5130,7 +5174,7 @@
         <v>74</v>
       </c>
       <c r="S38" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="T38" t="s" s="2">
         <v>74</v>
@@ -5169,7 +5213,7 @@
         <v>74</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -5189,17 +5233,17 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E39" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F39" t="s" s="2">
         <v>80</v>
@@ -5221,7 +5265,7 @@
       </c>
       <c r="L39" s="2"/>
       <c r="M39" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -5272,7 +5316,7 @@
         <v>74</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -5292,17 +5336,17 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E40" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F40" t="s" s="2">
         <v>75</v>
@@ -5311,7 +5355,7 @@
         <v>75</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>74</v>
@@ -5324,7 +5368,7 @@
       </c>
       <c r="L40" s="2"/>
       <c r="M40" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -5336,7 +5380,7 @@
         <v>74</v>
       </c>
       <c r="S40" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="T40" t="s" s="2">
         <v>74</v>
@@ -5375,7 +5419,7 @@
         <v>74</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -5395,10 +5439,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5421,11 +5465,11 @@
         <v>74</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="L41" s="2"/>
       <c r="M41" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -5476,7 +5520,7 @@
         <v>74</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -5496,10 +5540,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -5526,7 +5570,7 @@
       </c>
       <c r="L42" s="2"/>
       <c r="M42" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -5577,7 +5621,7 @@
         <v>74</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -5597,17 +5641,17 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E43" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F43" t="s" s="2">
         <v>80</v>
@@ -5625,11 +5669,11 @@
         <v>74</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="L43" s="2"/>
       <c r="M43" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -5680,7 +5724,7 @@
         <v>74</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -5700,17 +5744,17 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E44" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F44" t="s" s="2">
         <v>80</v>
@@ -5728,11 +5772,11 @@
         <v>74</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L44" s="2"/>
       <c r="M44" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -5783,7 +5827,7 @@
         <v>74</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -5803,17 +5847,17 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E45" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F45" t="s" s="2">
         <v>80</v>
@@ -5831,11 +5875,11 @@
         <v>74</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="L45" s="2"/>
       <c r="M45" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -5886,7 +5930,7 @@
         <v>74</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -5906,10 +5950,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -5923,7 +5967,7 @@
         <v>75</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>74</v>
@@ -5932,16 +5976,18 @@
         <v>74</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="N46" s="2"/>
-      <c r="O46" s="2"/>
+      <c r="O46" t="s" s="2">
+        <v>223</v>
+      </c>
       <c r="P46" t="s" s="2">
         <v>74</v>
       </c>
@@ -5989,7 +6035,7 @@
         <v>74</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -6009,10 +6055,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6026,7 +6072,7 @@
         <v>75</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>74</v>
@@ -6035,15 +6081,17 @@
         <v>74</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="N47" s="2"/>
+        <v>226</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>227</v>
+      </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>74</v>
@@ -6092,7 +6140,7 @@
         <v>74</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -6112,10 +6160,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6138,12 +6186,16 @@
         <v>74</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="L48" s="2"/>
+        <v>172</v>
+      </c>
+      <c r="L48" t="s" s="2">
+        <v>229</v>
+      </c>
       <c r="M48" s="2"/>
       <c r="N48" s="2"/>
-      <c r="O48" s="2"/>
+      <c r="O48" t="s" s="2">
+        <v>230</v>
+      </c>
       <c r="P48" t="s" s="2">
         <v>74</v>
       </c>
@@ -6191,7 +6243,7 @@
         <v>74</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -6211,10 +6263,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6239,10 +6291,14 @@
       <c r="K49" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="L49" s="2"/>
+      <c r="L49" t="s" s="2">
+        <v>232</v>
+      </c>
       <c r="M49" s="2"/>
       <c r="N49" s="2"/>
-      <c r="O49" s="2"/>
+      <c r="O49" t="s" s="2">
+        <v>233</v>
+      </c>
       <c r="P49" t="s" s="2">
         <v>74</v>
       </c>
@@ -6270,7 +6326,7 @@
       </c>
       <c r="Y49" s="2"/>
       <c r="Z49" t="s" s="2">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>74</v>
@@ -6288,7 +6344,7 @@
         <v>74</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -6308,10 +6364,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -6334,12 +6390,18 @@
         <v>74</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="L50" s="2"/>
+        <v>236</v>
+      </c>
+      <c r="L50" t="s" s="2">
+        <v>237</v>
+      </c>
       <c r="M50" s="2"/>
-      <c r="N50" s="2"/>
-      <c r="O50" s="2"/>
+      <c r="N50" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="O50" t="s" s="2">
+        <v>239</v>
+      </c>
       <c r="P50" t="s" s="2">
         <v>74</v>
       </c>
@@ -6387,7 +6449,7 @@
         <v>74</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -6407,10 +6469,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -6433,12 +6495,14 @@
         <v>74</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="L51" s="2"/>
       <c r="M51" s="2"/>
       <c r="N51" s="2"/>
-      <c r="O51" s="2"/>
+      <c r="O51" t="s" s="2">
+        <v>242</v>
+      </c>
       <c r="P51" t="s" s="2">
         <v>74</v>
       </c>
@@ -6486,7 +6550,7 @@
         <v>74</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -6506,10 +6570,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>232</v>
+        <v>243</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>232</v>
+        <v>243</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -6532,12 +6596,14 @@
         <v>74</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>233</v>
+        <v>244</v>
       </c>
       <c r="L52" s="2"/>
       <c r="M52" s="2"/>
       <c r="N52" s="2"/>
-      <c r="O52" s="2"/>
+      <c r="O52" t="s" s="2">
+        <v>245</v>
+      </c>
       <c r="P52" t="s" s="2">
         <v>74</v>
       </c>
@@ -6585,7 +6651,7 @@
         <v>74</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>232</v>
+        <v>243</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -6605,10 +6671,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>234</v>
+        <v>246</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>234</v>
+        <v>246</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -6622,7 +6688,7 @@
         <v>81</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>74</v>
@@ -6631,10 +6697,10 @@
         <v>74</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>236</v>
+        <v>248</v>
       </c>
       <c r="M53" s="2"/>
       <c r="N53" s="2"/>
@@ -6686,7 +6752,7 @@
         <v>74</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>234</v>
+        <v>246</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -6706,10 +6772,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>237</v>
+        <v>249</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>237</v>
+        <v>249</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -6807,10 +6873,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>238</v>
+        <v>250</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>238</v>
+        <v>250</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -6908,10 +6974,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>239</v>
+        <v>251</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>239</v>
+        <v>251</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7009,10 +7075,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>240</v>
+        <v>252</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>240</v>
+        <v>252</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7110,10 +7176,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -7213,10 +7279,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -7316,10 +7382,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -7419,10 +7485,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>244</v>
+        <v>256</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>244</v>
+        <v>256</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -7522,10 +7588,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -7623,10 +7689,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>246</v>
+        <v>258</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>246</v>
+        <v>258</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -7656,7 +7722,7 @@
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
-        <v>247</v>
+        <v>259</v>
       </c>
       <c r="Q63" s="2"/>
       <c r="R63" t="s" s="2">
@@ -7682,7 +7748,7 @@
       </c>
       <c r="Y63" s="2"/>
       <c r="Z63" t="s" s="2">
-        <v>248</v>
+        <v>260</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>74</v>
@@ -7700,7 +7766,7 @@
         <v>74</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -7720,10 +7786,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -7757,7 +7823,7 @@
       </c>
       <c r="Q64" s="2"/>
       <c r="R64" t="s" s="2">
-        <v>251</v>
+        <v>263</v>
       </c>
       <c r="S64" t="s" s="2">
         <v>74</v>
@@ -7799,7 +7865,7 @@
         <v>74</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>252</v>
+        <v>264</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -7819,10 +7885,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>253</v>
+        <v>265</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>253</v>
+        <v>265</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -7845,7 +7911,7 @@
         <v>74</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>254</v>
+        <v>266</v>
       </c>
       <c r="L65" s="2"/>
       <c r="M65" s="2"/>
@@ -7898,7 +7964,7 @@
         <v>74</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>255</v>
+        <v>267</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -7918,10 +7984,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>256</v>
+        <v>268</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>256</v>
+        <v>268</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -7944,7 +8010,7 @@
         <v>74</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>257</v>
+        <v>269</v>
       </c>
       <c r="L66" s="2"/>
       <c r="M66" s="2"/>
@@ -7997,7 +8063,7 @@
         <v>74</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>258</v>
+        <v>270</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -8017,10 +8083,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>259</v>
+        <v>271</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>259</v>
+        <v>271</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -8043,7 +8109,7 @@
         <v>74</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>260</v>
+        <v>272</v>
       </c>
       <c r="L67" s="2"/>
       <c r="M67" s="2"/>
@@ -8096,7 +8162,7 @@
         <v>74</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -8116,10 +8182,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>262</v>
+        <v>274</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>262</v>
+        <v>274</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -8142,7 +8208,7 @@
         <v>74</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>263</v>
+        <v>275</v>
       </c>
       <c r="L68" s="2"/>
       <c r="M68" s="2"/>
@@ -8195,7 +8261,7 @@
         <v>74</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>264</v>
+        <v>276</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -8215,10 +8281,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>265</v>
+        <v>277</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>265</v>
+        <v>277</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -8241,7 +8307,7 @@
         <v>74</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>266</v>
+        <v>278</v>
       </c>
       <c r="L69" s="2"/>
       <c r="M69" s="2"/>
@@ -8294,7 +8360,7 @@
         <v>74</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>267</v>
+        <v>279</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -8314,10 +8380,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>268</v>
+        <v>280</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>268</v>
+        <v>280</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -8340,7 +8406,7 @@
         <v>74</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>269</v>
+        <v>281</v>
       </c>
       <c r="L70" s="2"/>
       <c r="M70" s="2"/>
@@ -8393,7 +8459,7 @@
         <v>74</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>270</v>
+        <v>282</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -8413,10 +8479,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -8439,7 +8505,7 @@
         <v>74</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="L71" s="2"/>
       <c r="M71" s="2"/>
@@ -8492,7 +8558,7 @@
         <v>74</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -8512,10 +8578,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>274</v>
+        <v>286</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>274</v>
+        <v>286</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -8538,7 +8604,7 @@
         <v>74</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>275</v>
+        <v>287</v>
       </c>
       <c r="L72" s="2"/>
       <c r="M72" s="2"/>
@@ -8591,7 +8657,7 @@
         <v>74</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -8611,10 +8677,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>277</v>
+        <v>289</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>277</v>
+        <v>289</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -8637,7 +8703,7 @@
         <v>74</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>278</v>
+        <v>290</v>
       </c>
       <c r="L73" s="2"/>
       <c r="M73" s="2"/>
@@ -8690,7 +8756,7 @@
         <v>74</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>279</v>
+        <v>291</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -8710,10 +8776,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>280</v>
+        <v>292</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>280</v>
+        <v>292</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -8736,12 +8802,16 @@
         <v>74</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="L74" s="2"/>
+        <v>293</v>
+      </c>
+      <c r="L74" t="s" s="2">
+        <v>294</v>
+      </c>
       <c r="M74" s="2"/>
       <c r="N74" s="2"/>
-      <c r="O74" s="2"/>
+      <c r="O74" t="s" s="2">
+        <v>295</v>
+      </c>
       <c r="P74" t="s" s="2">
         <v>74</v>
       </c>
@@ -8789,7 +8859,7 @@
         <v>74</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>280</v>
+        <v>292</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -8809,10 +8879,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>282</v>
+        <v>296</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>282</v>
+        <v>296</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -8910,10 +8980,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>283</v>
+        <v>297</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>283</v>
+        <v>297</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -9011,10 +9081,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>284</v>
+        <v>298</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>284</v>
+        <v>298</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -9112,10 +9182,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>285</v>
+        <v>299</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>285</v>
+        <v>299</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -9213,10 +9283,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>286</v>
+        <v>300</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>286</v>
+        <v>300</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -9316,10 +9386,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>287</v>
+        <v>301</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>287</v>
+        <v>301</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -9419,10 +9489,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>288</v>
+        <v>302</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>288</v>
+        <v>302</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -9522,10 +9592,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>289</v>
+        <v>303</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>289</v>
+        <v>303</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -9625,10 +9695,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>290</v>
+        <v>304</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>290</v>
+        <v>304</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -9726,10 +9796,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>291</v>
+        <v>305</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>291</v>
+        <v>305</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -9756,7 +9826,7 @@
       </c>
       <c r="L84" s="2"/>
       <c r="M84" t="s" s="2">
-        <v>292</v>
+        <v>306</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -9765,7 +9835,7 @@
       </c>
       <c r="Q84" s="2"/>
       <c r="R84" t="s" s="2">
-        <v>247</v>
+        <v>259</v>
       </c>
       <c r="S84" t="s" s="2">
         <v>74</v>
@@ -9807,7 +9877,7 @@
         <v>74</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>291</v>
+        <v>305</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -9827,10 +9897,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>293</v>
+        <v>307</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>293</v>
+        <v>307</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -9864,7 +9934,7 @@
       </c>
       <c r="Q85" s="2"/>
       <c r="R85" t="s" s="2">
-        <v>251</v>
+        <v>263</v>
       </c>
       <c r="S85" t="s" s="2">
         <v>74</v>
@@ -9906,7 +9976,7 @@
         <v>74</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>293</v>
+        <v>307</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -9926,10 +9996,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>294</v>
+        <v>308</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>294</v>
+        <v>308</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -9952,7 +10022,7 @@
         <v>74</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>295</v>
+        <v>309</v>
       </c>
       <c r="L86" s="2"/>
       <c r="M86" s="2"/>
@@ -10005,7 +10075,7 @@
         <v>74</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>294</v>
+        <v>308</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>75</v>

--- a/main/ig/StructureDefinition-fr-cda-traitements.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-traitements.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T14:20:03+00:00</t>
+    <t>2026-06-29T15:28:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-traitements.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-traitements.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T15:28:29+00:00</t>
+    <t>2026-06-30T08:01:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-traitements.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-traitements.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T08:01:58+00:00</t>
+    <t>2026-06-30T09:01:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-traitements.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-traitements.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T09:01:37+00:00</t>
+    <t>2026-06-30T09:56:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-traitements.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-traitements.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T09:56:22+00:00</t>
+    <t>2026-08-06T11:33:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
